--- a/final_test/sales_data.xlsx
+++ b/final_test/sales_data.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21720" windowHeight="11660"/>
+    <workbookView windowWidth="22860" windowHeight="11600" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="test1" sheetId="3" r:id="rId3"/>
+    <sheet name="test2" sheetId="4" r:id="rId4"/>
+    <sheet name="test3" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="20">
   <si>
     <t>日期</t>
   </si>
@@ -82,6 +85,12 @@
   </si>
   <si>
     <t>最低产品销量</t>
+  </si>
+  <si>
+    <t>销售数</t>
+  </si>
+  <si>
+    <t>地区</t>
   </si>
 </sst>
 </file>
@@ -724,13 +733,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1267,11 +1276,11 @@
   <dimension ref="A1:E53"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="3"/>
+    <col min="1" max="1" width="9.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1288,7 +1297,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>46050</v>
       </c>
       <c r="B2" t="s">
@@ -1305,7 +1314,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>46027</v>
       </c>
       <c r="B3" t="s">
@@ -1322,7 +1331,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>46042</v>
       </c>
       <c r="B4" t="s">
@@ -1339,7 +1348,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>46031</v>
       </c>
       <c r="B5" t="s">
@@ -1356,7 +1365,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>46033</v>
       </c>
       <c r="B6" t="s">
@@ -1373,7 +1382,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>46026</v>
       </c>
       <c r="B7" t="s">
@@ -1390,7 +1399,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>46025</v>
       </c>
       <c r="B8" t="s">
@@ -1407,7 +1416,7 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>46025</v>
       </c>
       <c r="B9" t="s">
@@ -1424,7 +1433,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>46043</v>
       </c>
       <c r="B10" t="s">
@@ -1441,7 +1450,7 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>46032</v>
       </c>
       <c r="B11" t="s">
@@ -1458,7 +1467,7 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>46041</v>
       </c>
       <c r="B12" t="s">
@@ -1475,7 +1484,7 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>46033</v>
       </c>
       <c r="B13" t="s">
@@ -1492,7 +1501,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>46034</v>
       </c>
       <c r="B14" t="s">
@@ -1509,7 +1518,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>46025</v>
       </c>
       <c r="B15" t="s">
@@ -1526,7 +1535,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>46034</v>
       </c>
       <c r="B16" t="s">
@@ -1543,7 +1552,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>46039</v>
       </c>
       <c r="B17" t="s">
@@ -1560,7 +1569,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>46041</v>
       </c>
       <c r="B18" t="s">
@@ -1577,7 +1586,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>46043</v>
       </c>
       <c r="B19" t="s">
@@ -1594,7 +1603,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>46031</v>
       </c>
       <c r="B20" t="s">
@@ -1611,7 +1620,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>46047</v>
       </c>
       <c r="B21" t="s">
@@ -1628,7 +1637,7 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>46042</v>
       </c>
       <c r="B22" t="s">
@@ -1645,7 +1654,7 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3">
+      <c r="A23" s="1">
         <v>46030</v>
       </c>
       <c r="B23" t="s">
@@ -1662,7 +1671,7 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>46029</v>
       </c>
       <c r="B24" t="s">
@@ -1679,7 +1688,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>46038</v>
       </c>
       <c r="B25" t="s">
@@ -1696,7 +1705,7 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>46023</v>
       </c>
       <c r="B26" t="s">
@@ -1713,7 +1722,7 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>46041</v>
       </c>
       <c r="B27" t="s">
@@ -1724,7 +1733,7 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>46044</v>
       </c>
       <c r="B28" t="s">
@@ -1741,7 +1750,7 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>46043</v>
       </c>
       <c r="B29" t="s">
@@ -1758,7 +1767,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>46039</v>
       </c>
       <c r="B30" t="s">
@@ -1775,7 +1784,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>46047</v>
       </c>
       <c r="B31" t="s">
@@ -1792,7 +1801,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3">
+      <c r="A32" s="1">
         <v>46026</v>
       </c>
       <c r="B32" t="s">
@@ -1809,7 +1818,7 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>46034</v>
       </c>
       <c r="B33" t="s">
@@ -1826,7 +1835,7 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="3">
+      <c r="A34" s="1">
         <v>46033</v>
       </c>
       <c r="B34" t="s">
@@ -1843,7 +1852,7 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="3">
+      <c r="A35" s="1">
         <v>46048</v>
       </c>
       <c r="B35" t="s">
@@ -1860,7 +1869,7 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="3">
+      <c r="A36" s="1">
         <v>46039</v>
       </c>
       <c r="B36" t="s">
@@ -1877,7 +1886,7 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>46037</v>
       </c>
       <c r="B37" t="s">
@@ -1894,7 +1903,7 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="3">
+      <c r="A38" s="1">
         <v>46036</v>
       </c>
       <c r="B38" t="s">
@@ -1911,7 +1920,7 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="3">
+      <c r="A39" s="1">
         <v>46040</v>
       </c>
       <c r="B39" t="s">
@@ -1928,7 +1937,7 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="3">
+      <c r="A40" s="1">
         <v>46039</v>
       </c>
       <c r="B40" t="s">
@@ -1945,7 +1954,7 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="3">
+      <c r="A41" s="1">
         <v>46039</v>
       </c>
       <c r="B41" t="s">
@@ -1962,7 +1971,7 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="3">
+      <c r="A42" s="1">
         <v>46029</v>
       </c>
       <c r="B42" t="s">
@@ -1979,7 +1988,7 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="3">
+      <c r="A43" s="1">
         <v>46043</v>
       </c>
       <c r="B43" t="s">
@@ -1996,7 +2005,7 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="3">
+      <c r="A44" s="1">
         <v>46027</v>
       </c>
       <c r="B44" t="s">
@@ -2013,7 +2022,7 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="3">
+      <c r="A45" s="1">
         <v>46030</v>
       </c>
       <c r="B45" t="s">
@@ -2030,7 +2039,7 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="3">
+      <c r="A46" s="1">
         <v>46050</v>
       </c>
       <c r="B46" t="s">
@@ -2047,7 +2056,7 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="3">
+      <c r="A47" s="1">
         <v>46040</v>
       </c>
       <c r="B47" t="s">
@@ -2064,7 +2073,7 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="3">
+      <c r="A48" s="1">
         <v>46043</v>
       </c>
       <c r="B48" t="s">
@@ -2081,7 +2090,7 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="3">
+      <c r="A49" s="1">
         <v>46028</v>
       </c>
       <c r="B49" t="s">
@@ -2098,7 +2107,7 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="3">
+      <c r="A50" s="1">
         <v>46032</v>
       </c>
       <c r="B50" t="s">
@@ -2115,7 +2124,7 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="3">
+      <c r="A51" s="1">
         <v>46049</v>
       </c>
       <c r="B51" t="s">
@@ -2132,7 +2141,7 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="3">
+      <c r="A52" s="1">
         <v>46034</v>
       </c>
       <c r="B52" t="s">
@@ -2149,7 +2158,7 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="3">
+      <c r="A53" s="1">
         <v>46028</v>
       </c>
       <c r="B53" t="s">
@@ -2178,101 +2187,2729 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3">
+        <v>107</v>
+      </c>
+      <c r="D2" s="3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3">
+        <v>17.3333333333333</v>
+      </c>
+      <c r="C3" s="3">
+        <v>59</v>
+      </c>
+      <c r="D3" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
+        <v>25.1111111111111</v>
+      </c>
+      <c r="C4" s="3">
+        <v>121</v>
+      </c>
+      <c r="D4" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3">
+        <v>18.4545454545454</v>
+      </c>
+      <c r="C5" s="3">
+        <v>69</v>
+      </c>
+      <c r="D5" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3">
+        <v>25.25</v>
+      </c>
+      <c r="C6" s="3">
+        <v>84</v>
+      </c>
+      <c r="D6" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>21.6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>59</v>
+      </c>
+      <c r="D7" s="3">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2"/>
+      <c r="E2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5"/>
+      <c r="E5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6"/>
+      <c r="E6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7"/>
+      <c r="E7">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15"/>
+      <c r="E15">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16"/>
+      <c r="E16">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17"/>
+      <c r="E17">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18"/>
+      <c r="E18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19"/>
+      <c r="E19">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20"/>
+      <c r="E20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21"/>
+      <c r="E21">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22"/>
+      <c r="E22">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23"/>
+      <c r="E23">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24"/>
+      <c r="E24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25"/>
+      <c r="E25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26"/>
+      <c r="E26">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28"/>
+      <c r="E28">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29"/>
+      <c r="E29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30"/>
+      <c r="E30">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31"/>
+      <c r="E31">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32"/>
+      <c r="E32">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33"/>
+      <c r="E33">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34"/>
+      <c r="E34">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35"/>
+      <c r="E35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36"/>
+      <c r="E36">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37"/>
+      <c r="E37">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38"/>
+      <c r="E38">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39"/>
+      <c r="E39">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40"/>
+      <c r="E40">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41"/>
+      <c r="E41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42"/>
+      <c r="E42">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43"/>
+      <c r="E43">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44"/>
+      <c r="E44">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45"/>
+      <c r="E45">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46"/>
+      <c r="E46">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47"/>
+      <c r="E47">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48"/>
+      <c r="E48">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49"/>
+      <c r="E49">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50"/>
+      <c r="E50">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51"/>
+      <c r="E51">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52"/>
+      <c r="E52">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53"/>
+      <c r="E53">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>41</v>
+      </c>
+      <c r="E8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>25</v>
+      </c>
+      <c r="E12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>37</v>
+      </c>
+      <c r="E13">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="E15">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>29</v>
+      </c>
+      <c r="E17">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>36</v>
+      </c>
+      <c r="E18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B22" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
-        <v>34</v>
-      </c>
-      <c r="C2" s="2">
-        <v>107</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>44</v>
+      </c>
+      <c r="E22">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>11</v>
+      </c>
+      <c r="E24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>47</v>
+      </c>
+      <c r="E25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>28</v>
+      </c>
+      <c r="E28">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>31</v>
+      </c>
+      <c r="E29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31">
+        <v>25</v>
+      </c>
+      <c r="E31">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32">
+        <v>44</v>
+      </c>
+      <c r="E32">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33">
+        <v>25</v>
+      </c>
+      <c r="E33">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <v>45</v>
+      </c>
+      <c r="E34">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36">
+        <v>40</v>
+      </c>
+      <c r="E36">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37">
+        <v>30</v>
+      </c>
+      <c r="E37">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38">
+        <v>49</v>
+      </c>
+      <c r="E38">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39">
+        <v>8</v>
+      </c>
+      <c r="E39">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41">
+        <v>29</v>
+      </c>
+      <c r="E41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42">
+        <v>19</v>
+      </c>
+      <c r="E42">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>38</v>
+      </c>
+      <c r="E43">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44">
+        <v>26</v>
+      </c>
+      <c r="E44">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45">
+        <v>8</v>
+      </c>
+      <c r="E45">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46">
+        <v>50</v>
+      </c>
+      <c r="E46">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47">
+        <v>8</v>
+      </c>
+      <c r="E47">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48">
+        <v>46</v>
+      </c>
+      <c r="E48">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <v>11</v>
+      </c>
+      <c r="E49">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50">
+        <v>30</v>
+      </c>
+      <c r="E50">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51">
+        <v>38</v>
+      </c>
+      <c r="E51">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <v>16</v>
+      </c>
+      <c r="E53">
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="E2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2">
-        <v>17.3333333333333</v>
-      </c>
-      <c r="C3" s="2">
-        <v>59</v>
-      </c>
-      <c r="D3" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>41</v>
+      </c>
+      <c r="E8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>25</v>
+      </c>
+      <c r="E12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>37</v>
+      </c>
+      <c r="E13">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>16</v>
+      </c>
+      <c r="E15">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>29</v>
+      </c>
+      <c r="E17">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B18" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>25.1111111111111</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>36</v>
+      </c>
+      <c r="E18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>44</v>
+      </c>
+      <c r="E22">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>11</v>
+      </c>
+      <c r="E24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>47</v>
+      </c>
+      <c r="E25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>28</v>
+      </c>
+      <c r="E28">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>31</v>
+      </c>
+      <c r="E29">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31">
+        <v>25</v>
+      </c>
+      <c r="E31">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32">
+        <v>44</v>
+      </c>
+      <c r="E32">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33">
+        <v>25</v>
+      </c>
+      <c r="E33">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <v>45</v>
+      </c>
+      <c r="E34">
         <v>121</v>
       </c>
-      <c r="D4" s="2">
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36">
+        <v>40</v>
+      </c>
+      <c r="E36">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2">
-        <v>18.4545454545454</v>
-      </c>
-      <c r="C5" s="2">
-        <v>69</v>
-      </c>
-      <c r="D5" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="E37">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38">
+        <v>49</v>
+      </c>
+      <c r="E38">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39">
+        <v>8</v>
+      </c>
+      <c r="E39">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41">
+        <v>29</v>
+      </c>
+      <c r="E41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B42" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2">
-        <v>25.25</v>
-      </c>
-      <c r="C6" s="2">
-        <v>84</v>
-      </c>
-      <c r="D6" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2">
-        <v>21.6</v>
-      </c>
-      <c r="C7" s="2">
-        <v>59</v>
-      </c>
-      <c r="D7" s="2">
-        <v>49</v>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42">
+        <v>19</v>
+      </c>
+      <c r="E42">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>38</v>
+      </c>
+      <c r="E43">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44">
+        <v>26</v>
+      </c>
+      <c r="E44">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45">
+        <v>8</v>
+      </c>
+      <c r="E45">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46">
+        <v>50</v>
+      </c>
+      <c r="E46">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47">
+        <v>8</v>
+      </c>
+      <c r="E47">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48">
+        <v>46</v>
+      </c>
+      <c r="E48">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <v>11</v>
+      </c>
+      <c r="E49">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50">
+        <v>30</v>
+      </c>
+      <c r="E50">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51">
+        <v>38</v>
+      </c>
+      <c r="E51">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <v>16</v>
+      </c>
+      <c r="E53">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
